--- a/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt1_rubricas.xlsx
@@ -1896,13 +1896,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F99FD6BC-825E-44CB-AC2C-C54F87CBB9EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D6BBCB3-E9E6-45DF-AEA7-9BA195260705}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE729B54-D547-4392-8484-0FFC316769EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CF2FB0-1E9F-4D97-93CE-FEFBAAACEE44}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCB66821-D49E-4C1A-8F0E-658780D0E193}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FE67056-C8E2-40B0-9C0A-E7D26E535169}"/>
 </file>